--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-08-2025.xlsx
@@ -589,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -710,27 +710,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -831,27 +831,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -952,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1073,27 +1073,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1194,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-ga4070-2400x1200x70mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1315,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-ga4075-2400x1200x75mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1436,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-ga4080-2400x1200x80mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1557,27 +1557,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-ga4090-2400x1200x90mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1678,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-ga4100-2400x1200x100mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4110-insulation-2400x1200x110mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1920,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4120-2400x1200x120mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2041,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4130-2400x1200x130mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2162,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4140-2400x1200x140mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2283,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-xr4150-2400x1200x150mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3106,27 +3106,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3227,27 +3227,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3348,27 +3348,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3469,27 +3469,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7088be415+77285]
-	GetHandleVerifier [0x0x7ff7088be470+77376]
-	(No symbol) [0x0x7ff708689a6a]
-	(No symbol) [0x0x7ff7086e0406]
-	(No symbol) [0x0x7ff7086e06bc]
-	(No symbol) [0x0x7ff708733ac7]
-	(No symbol) [0x0x7ff70870864f]
-	(No symbol) [0x0x7ff70873087f]
-	(No symbol) [0x0x7ff7087083e3]
-	(No symbol) [0x0x7ff7086d1521]
-	(No symbol) [0x0x7ff7086d22b3]
-	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
-	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
-	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
-	GetHandleVerifier [0x0x7ff7088d884e+184862]
-	GetHandleVerifier [0x0x7ff7088e055f+216879]
-	GetHandleVerifier [0x0x7ff7088c7084+113236]
-	GetHandleVerifier [0x0x7ff7088c7239+113673]
-	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	GetHandleVerifier [0x0x7ff616f9e415+77285]
+	GetHandleVerifier [0x0x7ff616f9e470+77376]
+	(No symbol) [0x0x7ff616d69a6a]
+	(No symbol) [0x0x7ff616dc0406]
+	(No symbol) [0x0x7ff616dc06bc]
+	(No symbol) [0x0x7ff616e13ac7]
+	(No symbol) [0x0x7ff616de864f]
+	(No symbol) [0x0x7ff616e1087f]
+	(No symbol) [0x0x7ff616de83e3]
+	(No symbol) [0x0x7ff616db1521]
+	(No symbol) [0x0x7ff616db22b3]
+	GetHandleVerifier [0x0x7ff617281efd+3107021]
+	GetHandleVerifier [0x0x7ff61727c29d+3083373]
+	GetHandleVerifier [0x0x7ff61729bedd+3213485]
+	GetHandleVerifier [0x0x7ff616fb884e+184862]
+	GetHandleVerifier [0x0x7ff616fc055f+216879]
+	GetHandleVerifier [0x0x7ff616fa7084+113236]
+	GetHandleVerifier [0x0x7ff616fa7239+113673]
+	GetHandleVerifier [0x0x7ff616f8e298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 525 Server Error: &lt;none&gt; for url: https://www.directinsulation.com/product-page/celotex-cavity-cw4100-450mm-x-1200mm-pack-of-6</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
